--- a/resolveIssues/ig/StructureDefinition-fr-observation-vital-signs-document.xlsx
+++ b/resolveIssues/ig/StructureDefinition-fr-observation-vital-signs-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T07:56:38+00:00</t>
+    <t>2026-06-04T08:54:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/resolveIssues/ig/StructureDefinition-fr-observation-vital-signs-document.xlsx
+++ b/resolveIssues/ig/StructureDefinition-fr-observation-vital-signs-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T08:54:45+00:00</t>
+    <t>2026-06-04T14:47:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1884,7 +1884,7 @@
     <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/observation.html#notes) below.</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-value-set-ucum-document</t>
+    <t>http://terminology.hl7.org/ValueSet/ucum-units</t>
   </si>
   <si>
     <t xml:space="preserve">vs-3
@@ -2274,7 +2274,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="54.6171875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="69.015625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="67.2421875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
